--- a/docs/KitchenPluss AI Integration Plan.xlsx
+++ b/docs/KitchenPluss AI Integration Plan.xlsx
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/docs/KitchenPluss AI Integration Plan.xlsx
+++ b/docs/KitchenPluss AI Integration Plan.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
